--- a/output/tables/port_stats_1_130_30.xlsx
+++ b/output/tables/port_stats_1_130_30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,48 +662,64 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>B_UMD</t>
+          <t>t_HML</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3648363821556061</v>
+        <v>7.998270429429073</v>
       </c>
       <c r="C15" t="n">
-        <v>0.07632096924953821</v>
+        <v>1.515068352188926</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1378853239804816</v>
+        <v>7.334194901419076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>t_UMD</t>
+          <t>B_UMD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-3.206305469441445</v>
+        <v>-0.3648363821556061</v>
       </c>
       <c r="C16" t="n">
-        <v>1.638225946142962</v>
+        <v>0.07632096924953821</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.4830607748189</v>
+        <v>-0.1378853239804816</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>t_UMD</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-3.206305469441445</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.638225946142962</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.4830607748189</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>R_SQUARED</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>0.7152885280862014</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>0.4708399429007062</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>0.591380641179256</v>
       </c>
     </row>
